--- a/df_fPC1/sum.var_AMR_ville_C3G_R.xlsx
+++ b/df_fPC1/sum.var_AMR_ville_C3G_R.xlsx
@@ -635,7 +635,7 @@
         <v>-0.0757500947291418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.10036063159044</v>
+        <v>0.103147603373179</v>
       </c>
       <c r="G2" t="n">
         <v>0.0335610808107989</v>
@@ -757,7 +757,7 @@
         <v>0.00896430553400415</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0352159793973484</v>
+        <v>0.0332841500048817</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0975259174762126</v>
@@ -879,7 +879,7 @@
         <v>0.0116350506174326</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.278648268623139</v>
+        <v>-0.288815238863085</v>
       </c>
       <c r="G4" t="n">
         <v>-0.37338220636912</v>
@@ -1001,7 +1001,7 @@
         <v>-0.0856219006310501</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.046366232871423</v>
+        <v>-0.0408288727958792</v>
       </c>
       <c r="G5" t="n">
         <v>-0.130678648965293</v>
@@ -1123,7 +1123,7 @@
         <v>-0.0410338671533221</v>
       </c>
       <c r="F6" t="n">
-        <v>0.183072132285433</v>
+        <v>0.183906858976229</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0140515295826258</v>
@@ -1245,7 +1245,7 @@
         <v>0.110606121684165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0601744798308835</v>
+        <v>0.0530386693634788</v>
       </c>
       <c r="G7" t="n">
         <v>-0.188331569638821</v>
@@ -1367,7 +1367,7 @@
         <v>-0.0041952574902393</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0883645155060498</v>
+        <v>-0.0853534747701536</v>
       </c>
       <c r="G8" t="n">
         <v>0.309219299525867</v>
@@ -1489,7 +1489,7 @@
         <v>0.0962525363404283</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0504734259398501</v>
+        <v>0.0546274119630951</v>
       </c>
       <c r="G9" t="n">
         <v>-0.208271122741779</v>
@@ -1611,7 +1611,7 @@
         <v>0.0395856823912233</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0849547857042242</v>
+        <v>0.0851385988275439</v>
       </c>
       <c r="G10" t="n">
         <v>0.0601430323680632</v>
@@ -1733,7 +1733,7 @@
         <v>0.00953556340121431</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0158617624856274</v>
+        <v>0.0110290195894473</v>
       </c>
       <c r="G11" t="n">
         <v>0.313060253546427</v>
@@ -1855,7 +1855,7 @@
         <v>0.0151993913420284</v>
       </c>
       <c r="F12" t="n">
-        <v>0.12082021118173</v>
+        <v>0.126087432551128</v>
       </c>
       <c r="G12" t="n">
         <v>0.467253145695357</v>
@@ -1977,7 +1977,7 @@
         <v>-0.0851775313067445</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.237554391414924</v>
+        <v>-0.235262158219865</v>
       </c>
       <c r="G13" t="n">
         <v>-0.170995817172662</v>
